--- a/data/gst/schema/public/unregistered-applicants/v1.0/fields.xlsx
+++ b/data/gst/schema/public/unregistered-applicants/v1.0/fields.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
   <si>
     <t>Parameter Name</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Enrolment Number</t>
+  </si>
+  <si>
+    <t>Enrolment Number of the Unregistered Applicant</t>
   </si>
 </sst>
 </file>
@@ -1314,9 +1320,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" ns3:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.7265625" customWidth="1"/>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
@@ -1324,7 +1330,7 @@
     <col min="4" max="4" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ns3:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1338,12 +1344,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ns3:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>17</v>
@@ -1352,7 +1358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ns3:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>18</v>
       </c>
@@ -1368,7 +1374,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
 
